--- a/questionnaire_templates/013_group_trip_planning_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/013_group_trip_planning_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>trip_preferences</t>
+          <t>trip_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What do you prefer</t>
+          <t>What type of vacation are you looking for?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>trip_dates</t>
+          <t>trip_duration</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>When would you like to go</t>
+          <t>How long would you like to stay?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is your budget</t>
+          <t>What is your budget for the trip?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>trip_prio</t>
+          <t>trip_priority</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your priority</t>
+          <t>What is your priority for this trip?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,19 +612,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>travel_destinations</t>
+          <t>trip_destinations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which destinations</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Which destinations are you interested in visiting?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trip_duration</t>
+          <t>trip_durations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How long would you like to stay</t>
+          <t>What is your expected trip duration?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trip_budget_2</t>
+          <t>trip_budgets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your budget</t>
+          <t>What is your expected travel budget?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trip_prio_2</t>
+          <t>trip_priority_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your priority</t>
+          <t>How important is it for you to have a priority on this trip?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trip_preferences_2</t>
+          <t>group_size</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What do you prefer</t>
+          <t>How many people will you be traveling with?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trip_prio_3</t>
+          <t>travel_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your priority</t>
+          <t>How often do you plan to travel?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trip_destinations_2</t>
+          <t>travel_mode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Which destinations</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Are you planning a solo trip or with a group?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -776,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>trip_durations_2</t>
+          <t>travel_language</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How long</t>
+          <t>How many languages do you speak fluently?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trip_prio_4</t>
+          <t>travel_insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your priority</t>
+          <t>Are you planning to book travel insurance?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,24 +814,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>trip_destinations_3</t>
+          <t>daily_budget</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Which destinations</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>What is your expected daily budget per person?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -849,263 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>trip_durations_3</t>
+          <t>pool_importance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How long</t>
+          <t>How important is it for you to have a hotel with a pool?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>trip_prio_5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is your priority</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>trip_destinations_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Which destinations</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>trip_durations_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How long</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>trip_prio_6</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is your priority</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>trip_destinations_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Which destinations</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>trip_prio_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your priority</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>trip_durations_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How long</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>trip_prio_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is your priority</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>trip_destinations_7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Which destinations</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>trip_durations_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How long</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1122,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1150,714 +896,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trip_prio_choices</t>
+          <t>trip_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_4_1':_'destination'}</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_4_1': 'Destination'}</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>trip_prio_choices</t>
+          <t>trip_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_4_2':_'budget'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_4_2': 'Budget'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trip_prio_choices</t>
+          <t>trip_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_4_3':_'duration'}</t>
+          <t>mountains</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_4_3': 'Duration'}</t>
+          <t>Mountains</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>travel_destinations_choices</t>
+          <t>trip_duration_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_5_1':_'beach'}</t>
+          <t>3_days</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_5_1': 'Beach'}</t>
+          <t>3 days</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>travel_destinations_choices</t>
+          <t>trip_duration_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option_5_2':_'city'}</t>
+          <t>5_days</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option_5_2': 'City'}</t>
+          <t>5 days</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>travel_destinations_choices</t>
+          <t>trip_duration_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option_5_3':_'mountains'}</t>
+          <t>7_days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option_5_3': 'Mountains'}</t>
+          <t>7 days</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trip_prio_2_choices</t>
+          <t>trip_budget_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option_8_1':_'destination'}</t>
+          <t>less_than_$500</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option_8_1': 'Destination'}</t>
+          <t>Less than $500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>trip_prio_2_choices</t>
+          <t>trip_budget_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option_8_2':_'budget'}</t>
+          <t>$500-$1000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option_8_2': 'Budget'}</t>
+          <t>$500-$1000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>trip_prio_2_choices</t>
+          <t>trip_budget_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option_8_3':_'duration'}</t>
+          <t>more_than_$1000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option_8_3': 'Duration'}</t>
+          <t>More than $1000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trip_prio_3_choices</t>
+          <t>trip_priority_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option_10_1':_'destination'}</t>
+          <t>destination</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option_10_1': 'Destination'}</t>
+          <t>Destination</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>trip_prio_3_choices</t>
+          <t>trip_priority_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option_10_2':_'budget'}</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option_10_2': 'Budget'}</t>
+          <t>Budget</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>trip_prio_3_choices</t>
+          <t>trip_priority_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option_10_3':_'duration'}</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option_10_3': 'Duration'}</t>
+          <t>Duration</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>trip_destinations_2_choices</t>
+          <t>trip_destinations_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option_11_1':_'beach'}</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option_11_1': 'Beach'}</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>trip_destinations_2_choices</t>
+          <t>trip_destinations_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option_11_2':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option_11_2': 'City'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>trip_destinations_2_choices</t>
+          <t>trip_destinations_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option_11_3':_'mountains'}</t>
+          <t>mountains</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option_11_3': 'Mountains'}</t>
+          <t>Mountains</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>trip_prio_4_choices</t>
+          <t>trip_durations_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option_13_1':_'destination'}</t>
+          <t>3_days</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option_13_1': 'Destination'}</t>
+          <t>3 days</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>trip_prio_4_choices</t>
+          <t>trip_durations_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option_13_2':_'budget'}</t>
+          <t>5_days</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option_13_2': 'Budget'}</t>
+          <t>5 days</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>trip_prio_4_choices</t>
+          <t>trip_durations_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option_13_3':_'duration'}</t>
+          <t>7_days</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option_13_3': 'Duration'}</t>
+          <t>7 days</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trip_destinations_3_choices</t>
+          <t>trip_budgets_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option_14_1':_'beach'}</t>
+          <t>less_than_$500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option_14_1': 'Beach'}</t>
+          <t>Less than $500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>trip_destinations_3_choices</t>
+          <t>trip_budgets_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option_14_2':_'city'}</t>
+          <t>$500-$1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option_14_2': 'City'}</t>
+          <t>$500-$1000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>trip_destinations_3_choices</t>
+          <t>trip_budgets_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option_14_3':_'mountains'}</t>
+          <t>more_than_$1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option_14_3': 'Mountains'}</t>
+          <t>More than $1000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>trip_prio_5_choices</t>
+          <t>trip_priority_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option_16_1':_'destination'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option_16_1': 'Destination'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>trip_prio_5_choices</t>
+          <t>trip_priority_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option_16_2':_'budget'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option_16_2': 'Budget'}</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trip_prio_5_choices</t>
+          <t>trip_priority_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option_16_3':_'duration'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option_16_3': 'Duration'}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>trip_destinations_4_choices</t>
+          <t>group_size_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option_17_1':_'beach'}</t>
+          <t>1-3_people</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option_17_1': 'Beach'}</t>
+          <t>1-3 people</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>trip_destinations_4_choices</t>
+          <t>group_size_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option_17_2':_'city'}</t>
+          <t>4-6_people</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option_17_2': 'City'}</t>
+          <t>4-6 people</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>trip_destinations_4_choices</t>
+          <t>group_size_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option_17_3':_'mountains'}</t>
+          <t>more_than_6_people</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option_17_3': 'Mountains'}</t>
+          <t>More than 6 people</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>trip_prio_6_choices</t>
+          <t>travel_frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option_19_1':_'destination'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option_19_1': 'Destination'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>trip_prio_6_choices</t>
+          <t>travel_frequency_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option_19_2':_'budget'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option_19_2': 'Budget'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>trip_prio_6_choices</t>
+          <t>travel_frequency_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option_19_3':_'duration'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option_19_3': 'Duration'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>trip_destinations_5_choices</t>
+          <t>pool_importance_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option_20_1':_'beach'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option_20_1': 'Beach'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>trip_destinations_5_choices</t>
+          <t>pool_importance_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option_20_2':_'city'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option_20_2': 'City'}</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>trip_destinations_5_choices</t>
+          <t>pool_importance_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option_20_3':_'mountains'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option_20_3': 'Mountains'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>trip_prio_7_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'option_21_1':_'destination'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'option_21_1': 'Destination'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>trip_prio_7_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'option_21_2':_'budget'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'option_21_2': 'Budget'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>trip_prio_7_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'option_21_3':_'duration'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'option_21_3': 'Duration'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>trip_prio_8_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'option_23_1':_'destination'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'option_23_1': 'Destination'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>trip_prio_8_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'option_23_2':_'budget'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'option_23_2': 'Budget'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>trip_prio_8_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'option_23_3':_'duration'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'option_23_3': 'Duration'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>trip_destinations_7_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'option_24_1':_'beach'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'option_24_1': 'Beach'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>trip_destinations_7_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'option_24_2':_'city'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'option_24_2': 'City'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>trip_destinations_7_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'option_24_3':_'mountains'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'option_24_3': 'Mountains'}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
